--- a/artfynd/A 42099-2025 artfynd.xlsx
+++ b/artfynd/A 42099-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -897,6 +897,220 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128436337</v>
+      </c>
+      <c r="B4" t="n">
+        <v>78790</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lisskogskölen, Lisskogskölen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>418228</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6707726</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Malung</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jon Eklund</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jon Eklund</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128437482</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lisskogskölen, Lisskogskölen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>418217</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6707717</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Malung</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jon Eklund</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jon Eklund</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42099-2025 artfynd.xlsx
+++ b/artfynd/A 42099-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>128436337</v>
       </c>
       <c r="B4" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>128437482</v>
       </c>
       <c r="B5" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 42099-2025 artfynd.xlsx
+++ b/artfynd/A 42099-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>128436337</v>
       </c>
       <c r="B4" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>128437482</v>
       </c>
       <c r="B5" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 42099-2025 artfynd.xlsx
+++ b/artfynd/A 42099-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>128436337</v>
       </c>
       <c r="B4" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>128437482</v>
       </c>
       <c r="B5" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 42099-2025 artfynd.xlsx
+++ b/artfynd/A 42099-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>128436337</v>
       </c>
       <c r="B4" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>128437482</v>
       </c>
       <c r="B5" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 42099-2025 artfynd.xlsx
+++ b/artfynd/A 42099-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>128436337</v>
       </c>
       <c r="B4" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>128437482</v>
       </c>
       <c r="B5" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 42099-2025 artfynd.xlsx
+++ b/artfynd/A 42099-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>128436337</v>
       </c>
       <c r="B4" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>128437482</v>
       </c>
       <c r="B5" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 42099-2025 artfynd.xlsx
+++ b/artfynd/A 42099-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>128436337</v>
       </c>
       <c r="B4" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>128437482</v>
       </c>
       <c r="B5" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 42099-2025 artfynd.xlsx
+++ b/artfynd/A 42099-2025 artfynd.xlsx
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>80491979</v>
+        <v>128436806</v>
       </c>
       <c r="B2" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gårmyran V om, Dlr</t>
+          <t>Lisskogskölen, Lisskogskölen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>418295.2510289202</v>
+        <v>418210</v>
       </c>
       <c r="R2" t="n">
-        <v>6707585.242216109</v>
+        <v>6707748</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-09-20</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-09-20</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,65 +770,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Jon Eklund</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Jon Eklund</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>80491980</v>
+        <v>128437482</v>
       </c>
       <c r="B3" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gårmyran V om, Dlr</t>
+          <t>Lisskogskölen, Lisskogskölen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>418295.2510289202</v>
+        <v>418217</v>
       </c>
       <c r="R3" t="n">
-        <v>6707585.242216109</v>
+        <v>6707717</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-09-20</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-09-20</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,22 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Jon Eklund</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Jon Eklund</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128436337</v>
+        <v>80491980</v>
       </c>
       <c r="B4" t="n">
-        <v>78786</v>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,17 +920,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lisskogskölen, Lisskogskölen, Dlr</t>
+          <t>Gårmyran V om, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>418228</v>
+        <v>418295</v>
       </c>
       <c r="R4" t="n">
-        <v>6707726</v>
+        <v>6707585</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,22 +954,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:18</t>
+          <t>2019-09-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:18</t>
+          <t>2019-09-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,22 +974,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jon Eklund</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jon Eklund</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128437482</v>
+        <v>80491979</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>79085</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,37 +997,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lisskogskölen, Lisskogskölen, Dlr</t>
+          <t>Gårmyran V om, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>418217</v>
+        <v>418295</v>
       </c>
       <c r="R5" t="n">
-        <v>6707717</v>
+        <v>6707585</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,22 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:31</t>
+          <t>2019-09-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:31</t>
+          <t>2019-09-20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,12 +1071,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jon Eklund</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jon Eklund</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 42099-2025 artfynd.xlsx
+++ b/artfynd/A 42099-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128436806</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128437482</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80491980</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,8 +1100,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80491979</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>